--- a/data/trans_orig/P1421-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2007</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32304</t>
+          <t>33087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256349</t>
+          <t>256772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268332</t>
+          <t>268967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239963</t>
+          <t>239462</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254682</t>
+          <t>254524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>501544</t>
+          <t>500761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520662</t>
+          <t>520355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32838</t>
+          <t>31859</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58168</t>
+          <t>56530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35331</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63758</t>
+          <t>63435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483121</t>
+          <t>483558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492003</t>
+          <t>492030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445781</t>
+          <t>447419</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>471111</t>
+          <t>472090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>933266</t>
+          <t>933589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>961693</t>
+          <t>959264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14154</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>30704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304692</t>
+          <t>303360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316201</t>
+          <t>316055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312980</t>
+          <t>313217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327430</t>
+          <t>327387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>623569</t>
+          <t>623554</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642039</t>
+          <t>641752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9722</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>32234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345167</t>
+          <t>344987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356058</t>
+          <t>355989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346300</t>
+          <t>346403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361734</t>
+          <t>362534</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696084</t>
+          <t>697893</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715421</t>
+          <t>716124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>13795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195796</t>
+          <t>195729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202395</t>
+          <t>202392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195216</t>
+          <t>193873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205505</t>
+          <t>205444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>393872</t>
+          <t>395072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406961</t>
+          <t>406949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>26170</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>17758</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37331</t>
+          <t>38293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252571</t>
+          <t>253658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266160</t>
+          <t>266217</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252047</t>
+          <t>251974</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267482</t>
+          <t>268014</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>511624</t>
+          <t>510662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532053</t>
+          <t>531197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18944</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36322</t>
+          <t>36623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>25638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50064</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596083</t>
+          <t>595917</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609478</t>
+          <t>609582</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>601897</t>
+          <t>601596</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>622018</t>
+          <t>621716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1203182</t>
+          <t>1203627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1227915</t>
+          <t>1227608</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40891</t>
+          <t>42579</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46166</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76595</t>
+          <t>76650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73184</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111023</t>
+          <t>110048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>702904</t>
+          <t>701216</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723864</t>
+          <t>724574</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>706916</t>
+          <t>706861</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>737345</t>
+          <t>736190</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1416283</t>
+          <t>1417258</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1454122</t>
+          <t>1455258</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>62180</t>
+          <t>62800</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97126</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>168059</t>
+          <t>170511</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>221885</t>
+          <t>224671</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>242222</t>
+          <t>243028</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>307169</t>
+          <t>305286</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3179417</t>
+          <t>3178313</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3214363</t>
+          <t>3213743</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3157312</t>
+          <t>3154526</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3211138</t>
+          <t>3208686</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6348572</t>
+          <t>6350455</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6413519</t>
+          <t>6412713</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2012</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>35058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41400</t>
+          <t>40179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283929</t>
+          <t>283893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292933</t>
+          <t>292947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252321</t>
+          <t>252187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271656</t>
+          <t>272696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540583</t>
+          <t>541804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563594</t>
+          <t>562561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37169</t>
+          <t>37354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>20619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43261</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491817</t>
+          <t>491723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503622</t>
+          <t>503629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486596</t>
+          <t>486411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507255</t>
+          <t>507544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>986031</t>
+          <t>986123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009783</t>
+          <t>1008673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29991</t>
+          <t>28322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313771</t>
+          <t>313592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322186</t>
+          <t>322181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318095</t>
+          <t>318318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333310</t>
+          <t>333693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>635075</t>
+          <t>636744</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653896</t>
+          <t>653758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48875</t>
+          <t>49243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29317</t>
+          <t>30093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54152</t>
+          <t>55686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361529</t>
+          <t>361173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371888</t>
+          <t>371167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340076</t>
+          <t>339708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363934</t>
+          <t>363299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708781</t>
+          <t>707247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>733616</t>
+          <t>732840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32201</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205146</t>
+          <t>204914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187390</t>
+          <t>188207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205571</t>
+          <t>205979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396461</t>
+          <t>397143</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>416031</t>
+          <t>416217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>27049</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261551</t>
+          <t>262094</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272053</t>
+          <t>272050</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257055</t>
+          <t>256872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270253</t>
+          <t>271146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523381</t>
+          <t>525028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540368</t>
+          <t>540478</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>16964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44858</t>
+          <t>44510</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29450</t>
+          <t>29333</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54872</t>
+          <t>53531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646463</t>
+          <t>645824</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658792</t>
+          <t>658497</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>648995</t>
+          <t>649343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>672879</t>
+          <t>673084</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1301769</t>
+          <t>1303110</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1327191</t>
+          <t>1327308</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>36326</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>42531</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>769005</t>
+          <t>768009</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777070</t>
+          <t>777055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>785782</t>
+          <t>786252</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>805963</t>
+          <t>805921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1558249</t>
+          <t>1558115</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1580608</t>
+          <t>1580120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>30012</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56895</t>
+          <t>55803</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>164439</t>
+          <t>166549</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>218165</t>
+          <t>217776</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>200918</t>
+          <t>202730</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>263521</t>
+          <t>263268</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3368853</t>
+          <t>3369945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3395479</t>
+          <t>3395736</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3336933</t>
+          <t>3337322</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3390659</t>
+          <t>3388549</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6717326</t>
+          <t>6717579</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6779929</t>
+          <t>6778117</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2016</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37059</t>
+          <t>38711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42374</t>
+          <t>42159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284716</t>
+          <t>285140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292797</t>
+          <t>292791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251644</t>
+          <t>249992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271578</t>
+          <t>271425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540090</t>
+          <t>540305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562559</t>
+          <t>563634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>30276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494653</t>
+          <t>494004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501720</t>
+          <t>501713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494608</t>
+          <t>494818</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511606</t>
+          <t>512140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>994299</t>
+          <t>995383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012185</t>
+          <t>1012674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21450</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313879</t>
+          <t>312978</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314859</t>
+          <t>314279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329369</t>
+          <t>329479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631840</t>
+          <t>632162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647431</t>
+          <t>647623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42554</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25107</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51490</t>
+          <t>50021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355858</t>
+          <t>356375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367032</t>
+          <t>366921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344729</t>
+          <t>344844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368314</t>
+          <t>368232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>705757</t>
+          <t>707226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732140</t>
+          <t>731771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28958</t>
+          <t>29085</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200697</t>
+          <t>201047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209340</t>
+          <t>209384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189629</t>
+          <t>189502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206387</t>
+          <t>206855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394511</t>
+          <t>394167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414054</t>
+          <t>414278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27104</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>32342</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250206</t>
+          <t>250317</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261060</t>
+          <t>261083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>246011</t>
+          <t>247245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263201</t>
+          <t>263712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503750</t>
+          <t>503896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>522533</t>
+          <t>523432</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54723</t>
+          <t>54224</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42072</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72465</t>
+          <t>72410</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632077</t>
+          <t>632369</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648061</t>
+          <t>647790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>636571</t>
+          <t>637070</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>662200</t>
+          <t>662829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275387</t>
+          <t>1275442</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1305780</t>
+          <t>1306581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23395</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30148</t>
+          <t>30469</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>57325</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762652</t>
+          <t>761804</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774520</t>
+          <t>773968</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>779088</t>
+          <t>778242</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>802772</t>
+          <t>804491</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1548994</t>
+          <t>1547425</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1574602</t>
+          <t>1574281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>35392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62504</t>
+          <t>62858</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>165825</t>
+          <t>169038</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>221531</t>
+          <t>225855</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>209681</t>
+          <t>211957</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>274692</t>
+          <t>280336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3331846</t>
+          <t>3331492</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3358606</t>
+          <t>3358958</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3323011</t>
+          <t>3318687</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3378717</t>
+          <t>3375504</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6664200</t>
+          <t>6658556</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6729211</t>
+          <t>6726935</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de migrañas en 2023</t>
+          <t>Población con diagnóstico de migrañas/ jaquecas / cefaleas crónicas / dolor de cabeza frecuente en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24056</t>
+          <t>24776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>41001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>33500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57280</t>
+          <t>56450</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288979</t>
+          <t>288635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306036</t>
+          <t>305373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249232</t>
+          <t>248634</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265579</t>
+          <t>264859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>543797</t>
+          <t>544627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568174</t>
+          <t>567577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49353</t>
+          <t>50278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58159</t>
+          <t>58061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87897</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86555</t>
+          <t>88362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129149</t>
+          <t>129406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468040</t>
+          <t>467115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494207</t>
+          <t>495433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425659</t>
+          <t>425582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455397</t>
+          <t>455495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>901800</t>
+          <t>901543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944394</t>
+          <t>942587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>33182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54651</t>
+          <t>55563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45431</t>
+          <t>46301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70940</t>
+          <t>71109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293034</t>
+          <t>291761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306457</t>
+          <t>307031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294477</t>
+          <t>293565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315901</t>
+          <t>315946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>594073</t>
+          <t>593904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>619582</t>
+          <t>618712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>21491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43782</t>
+          <t>42382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298106</t>
+          <t>298178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309167</t>
+          <t>308824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>440205</t>
+          <t>441061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>461622</t>
+          <t>460754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>744492</t>
+          <t>745892</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766628</t>
+          <t>766783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19369</t>
+          <t>20009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32636</t>
+          <t>33180</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>27867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45831</t>
+          <t>43994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162641</t>
+          <t>162754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172995</t>
+          <t>173237</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175638</t>
+          <t>175094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188905</t>
+          <t>188265</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341185</t>
+          <t>343022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359402</t>
+          <t>359149</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>24568</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29874</t>
+          <t>29224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47834</t>
+          <t>47131</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43992</t>
+          <t>44185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66985</t>
+          <t>67313</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243805</t>
+          <t>245068</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258268</t>
+          <t>258289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208553</t>
+          <t>209256</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226513</t>
+          <t>227163</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459038</t>
+          <t>458710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>482031</t>
+          <t>481838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34315</t>
+          <t>33343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66306</t>
+          <t>65643</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47504</t>
+          <t>52813</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152941</t>
+          <t>152683</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92461</t>
+          <t>97102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>191678</t>
+          <t>191601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>556198</t>
+          <t>556861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>588189</t>
+          <t>589161</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>694138</t>
+          <t>694396</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>799575</t>
+          <t>794266</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1277906</t>
+          <t>1277983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1377123</t>
+          <t>1372482</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31194</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>59678</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30219</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75235</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>911286</t>
+          <t>910581</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925400</t>
+          <t>925541</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>653214</t>
+          <t>655714</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>684198</t>
+          <t>684154</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1571606</t>
+          <t>1568877</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1613893</t>
+          <t>1611923</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>116210</t>
+          <t>115766</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>183145</t>
+          <t>182537</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>324136</t>
+          <t>325032</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>430274</t>
+          <t>430155</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>468767</t>
+          <t>470235</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>596982</t>
+          <t>597952</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3273735</t>
+          <t>3274343</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3340670</t>
+          <t>3341114</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3224894</t>
+          <t>3225013</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3331032</t>
+          <t>3330136</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6515066</t>
+          <t>6514096</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6643281</t>
+          <t>6641813</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1421-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1421-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33087</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256772</t>
+          <t>256750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268967</t>
+          <t>268610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239462</t>
+          <t>238334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254524</t>
+          <t>254195</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500761</t>
+          <t>502133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>520355</t>
+          <t>520499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56530</t>
+          <t>57525</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>36183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63435</t>
+          <t>63923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483558</t>
+          <t>483070</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492030</t>
+          <t>492008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447419</t>
+          <t>446424</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>472090</t>
+          <t>472392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>933589</t>
+          <t>933101</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959264</t>
+          <t>960841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15486</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303360</t>
+          <t>305539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316055</t>
+          <t>316145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313217</t>
+          <t>311450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327387</t>
+          <t>327366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>623554</t>
+          <t>623852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641752</t>
+          <t>641580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>24493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32234</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344987</t>
+          <t>344370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355989</t>
+          <t>356224</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346403</t>
+          <t>346963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362534</t>
+          <t>362033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697893</t>
+          <t>696727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716124</t>
+          <t>715629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>16329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195729</t>
+          <t>195896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202392</t>
+          <t>202404</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193873</t>
+          <t>195307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205444</t>
+          <t>205335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>395072</t>
+          <t>394647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>406949</t>
+          <t>406407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>25715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38293</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253658</t>
+          <t>253212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266217</t>
+          <t>266296</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251974</t>
+          <t>252429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268014</t>
+          <t>268223</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>510662</t>
+          <t>510459</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>531197</t>
+          <t>531213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36623</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25638</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49619</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595917</t>
+          <t>594894</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609582</t>
+          <t>609115</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>601596</t>
+          <t>601059</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>621716</t>
+          <t>621566</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1203627</t>
+          <t>1204386</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1227608</t>
+          <t>1227924</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42579</t>
+          <t>41240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47321</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76650</t>
+          <t>76524</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72048</t>
+          <t>73426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110048</t>
+          <t>110354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>701216</t>
+          <t>702555</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>724574</t>
+          <t>723428</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>706861</t>
+          <t>706987</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>736190</t>
+          <t>735719</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1417258</t>
+          <t>1416952</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1455258</t>
+          <t>1453880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>63733</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>98230</t>
+          <t>98843</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>170511</t>
+          <t>168324</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>224671</t>
+          <t>222270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>243028</t>
+          <t>241953</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>305286</t>
+          <t>304359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3178313</t>
+          <t>3177700</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3213743</t>
+          <t>3212810</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3154526</t>
+          <t>3156927</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3208686</t>
+          <t>3210873</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6350455</t>
+          <t>6351382</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6412713</t>
+          <t>6413788</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>35144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19422</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40179</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283893</t>
+          <t>282469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292947</t>
+          <t>292937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252187</t>
+          <t>252101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272696</t>
+          <t>272379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>541804</t>
+          <t>539377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562561</t>
+          <t>563572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13804</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37354</t>
+          <t>36278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491723</t>
+          <t>491610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503629</t>
+          <t>504483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486411</t>
+          <t>487487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>507544</t>
+          <t>507327</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>986123</t>
+          <t>985994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1008673</t>
+          <t>1009236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>22840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>27763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313592</t>
+          <t>313656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322181</t>
+          <t>322197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318318</t>
+          <t>318180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333693</t>
+          <t>333296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636744</t>
+          <t>637303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653758</t>
+          <t>653573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25652</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49243</t>
+          <t>47393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30093</t>
+          <t>30295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55686</t>
+          <t>56029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361173</t>
+          <t>360880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371167</t>
+          <t>371915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339708</t>
+          <t>341558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363299</t>
+          <t>364940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707247</t>
+          <t>706904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732840</t>
+          <t>732638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31384</t>
+          <t>32756</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35066</t>
+          <t>36808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204914</t>
+          <t>205841</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188207</t>
+          <t>186835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205979</t>
+          <t>205364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397143</t>
+          <t>395401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>416217</t>
+          <t>416429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21224</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262094</t>
+          <t>261618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272050</t>
+          <t>272144</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256872</t>
+          <t>256267</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271146</t>
+          <t>270295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525028</t>
+          <t>525091</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540478</t>
+          <t>541168</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29333</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645824</t>
+          <t>645927</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>658497</t>
+          <t>658678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>649343</t>
+          <t>649634</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>673084</t>
+          <t>673559</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1303110</t>
+          <t>1302241</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1327308</t>
+          <t>1328290</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36326</t>
+          <t>37718</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42531</t>
+          <t>43584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>768009</t>
+          <t>768171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777055</t>
+          <t>777041</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>786252</t>
+          <t>784860</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>805921</t>
+          <t>805469</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1558115</t>
+          <t>1557062</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1580120</t>
+          <t>1580404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30012</t>
+          <t>30091</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55803</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>166549</t>
+          <t>162510</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>217776</t>
+          <t>218997</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>202730</t>
+          <t>201953</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>263268</t>
+          <t>262877</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3369945</t>
+          <t>3369565</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3395736</t>
+          <t>3395657</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3337322</t>
+          <t>3336101</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3388549</t>
+          <t>3392588</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6717579</t>
+          <t>6717970</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6778117</t>
+          <t>6778894</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>37791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>19226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285140</t>
+          <t>285433</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292791</t>
+          <t>292810</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249992</t>
+          <t>250912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271425</t>
+          <t>271172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540305</t>
+          <t>540249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563634</t>
+          <t>563238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>27608</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>30944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494004</t>
+          <t>495175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501713</t>
+          <t>501721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494818</t>
+          <t>495476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512140</t>
+          <t>512398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>995383</t>
+          <t>994715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012674</t>
+          <t>1012202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312978</t>
+          <t>313960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314279</t>
+          <t>315125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329479</t>
+          <t>329703</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632162</t>
+          <t>632317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>647623</t>
+          <t>647253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>42881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25476</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50021</t>
+          <t>50634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356375</t>
+          <t>357015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366921</t>
+          <t>366936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344844</t>
+          <t>344402</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368232</t>
+          <t>367799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707226</t>
+          <t>706613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>731771</t>
+          <t>732957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>12582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35641</t>
+          <t>34119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201047</t>
+          <t>200757</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209384</t>
+          <t>209367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>189502</t>
+          <t>189915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206855</t>
+          <t>206005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>394167</t>
+          <t>395689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414278</t>
+          <t>413908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25870</t>
+          <t>25570</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>33250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250317</t>
+          <t>250178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261083</t>
+          <t>261008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247245</t>
+          <t>247545</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263712</t>
+          <t>263675</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503896</t>
+          <t>502988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523432</t>
+          <t>522172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54224</t>
+          <t>54184</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41271</t>
+          <t>41128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72410</t>
+          <t>72262</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632369</t>
+          <t>632165</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647790</t>
+          <t>648278</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637070</t>
+          <t>637110</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>662829</t>
+          <t>662885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275442</t>
+          <t>1275590</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1306581</t>
+          <t>1306724</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21676</t>
+          <t>23027</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47925</t>
+          <t>46707</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,47 +9830,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>42038</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>29848</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>56797</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>42038</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>30469</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>57325</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>761804</t>
+          <t>761634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773968</t>
+          <t>774021</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>778242</t>
+          <t>779460</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>804491</t>
+          <t>803140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,47 +9943,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1562712</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1547953</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1574902</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>97,38%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1562712</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1547425</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1574281</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35392</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62858</t>
+          <t>64238</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169038</t>
+          <t>166148</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>225855</t>
+          <t>223414</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211957</t>
+          <t>212211</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>280336</t>
+          <t>273862</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3331492</t>
+          <t>3330112</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3358958</t>
+          <t>3358735</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3318687</t>
+          <t>3321128</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3375504</t>
+          <t>3378394</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6658556</t>
+          <t>6665030</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6726935</t>
+          <t>6726681</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24776</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>45557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,27 +10767,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>46178</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56450</t>
+          <t>59587</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>299891</t>
+          <t>308255</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288635</t>
+          <t>300019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305373</t>
+          <t>313455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>257555</t>
+          <t>280473</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248634</t>
+          <t>270504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264859</t>
+          <t>289305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,22 +10880,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>557445</t>
+          <t>588728</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>544627</t>
+          <t>575319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567577</t>
+          <t>598533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>36041</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50278</t>
+          <t>53280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>75963</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58061</t>
+          <t>60287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87974</t>
+          <t>91551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>106698</t>
+          <t>112004</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88362</t>
+          <t>92854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>135874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>482980</t>
+          <t>493619</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467115</t>
+          <t>476380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495433</t>
+          <t>505452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>441271</t>
+          <t>469125</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425582</t>
+          <t>453537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455495</t>
+          <t>484801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>924251</t>
+          <t>962744</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>901543</t>
+          <t>938874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>942587</t>
+          <t>981894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513556</t>
+          <t>545088</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513556</t>
+          <t>545088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513556</t>
+          <t>545088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030949</t>
+          <t>1074748</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030949</t>
+          <t>1074748</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030949</t>
+          <t>1074748</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15073</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24124</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>44616</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>35635</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55563</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>57735</t>
+          <t>59689</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46301</t>
+          <t>48218</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71109</t>
+          <t>74653</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>300699</t>
+          <t>299183</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291761</t>
+          <t>290731</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307031</t>
+          <t>305271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>306579</t>
+          <t>311765</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293565</t>
+          <t>300521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315946</t>
+          <t>320746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>607278</t>
+          <t>610948</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>593904</t>
+          <t>595984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>618712</t>
+          <t>622419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315885</t>
+          <t>314256</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315885</t>
+          <t>314256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315885</t>
+          <t>314256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665013</t>
+          <t>670637</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665013</t>
+          <t>670637</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665013</t>
+          <t>670637</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>16833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>28855</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34657</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>27209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>46882</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>305299</t>
+          <t>365747</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298178</t>
+          <t>356312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308824</t>
+          <t>369762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>451050</t>
+          <t>393106</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441061</t>
+          <t>382834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460754</t>
+          <t>399923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>756348</t>
+          <t>758854</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745892</t>
+          <t>748225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766783</t>
+          <t>767898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15988</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25420</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20009</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>33408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>36475</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27867</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>46196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>169039</t>
+          <t>195353</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162754</t>
+          <t>188944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173237</t>
+          <t>199660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>182854</t>
+          <t>200660</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175094</t>
+          <t>193415</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188265</t>
+          <t>206707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>351893</t>
+          <t>396013</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>343022</t>
+          <t>386292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359149</t>
+          <t>403565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24568</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37513</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29224</t>
+          <t>30349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>48246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,17 +12482,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>54814</t>
+          <t>55599</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44185</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67313</t>
+          <t>67763</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>252335</t>
+          <t>253749</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245068</t>
+          <t>246255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258289</t>
+          <t>259167</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>218874</t>
+          <t>224458</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209256</t>
+          <t>214853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227163</t>
+          <t>232750</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,17 +12595,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>471209</t>
+          <t>478207</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>458710</t>
+          <t>466043</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>481838</t>
+          <t>488204</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>47641</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>37539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65643</t>
+          <t>71572</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>109286</t>
+          <t>129461</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52813</t>
+          <t>110827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152683</t>
+          <t>149234</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>156927</t>
+          <t>182445</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97102</t>
+          <t>158059</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>191601</t>
+          <t>211854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>574863</t>
+          <t>664739</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>556861</t>
+          <t>646151</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>589161</t>
+          <t>680184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>737793</t>
+          <t>639754</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>694396</t>
+          <t>619981</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>794266</t>
+          <t>658388</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1312657</t>
+          <t>1304493</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1277983</t>
+          <t>1275084</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1372482</t>
+          <t>1328879</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622504</t>
+          <t>717723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622504</t>
+          <t>717723</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622504</t>
+          <t>717723</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847079</t>
+          <t>769215</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847079</t>
+          <t>769215</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847079</t>
+          <t>769215</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1469584</t>
+          <t>1486938</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1469584</t>
+          <t>1486938</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1469584</t>
+          <t>1486938</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>19646</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>42323</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31238</t>
+          <t>32565</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59678</t>
+          <t>54617</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>51971</t>
+          <t>54075</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32189</t>
+          <t>41255</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75235</t>
+          <t>69500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>919072</t>
+          <t>787165</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>910581</t>
+          <t>778426</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925541</t>
+          <t>792344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>673069</t>
+          <t>787441</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>655714</t>
+          <t>775992</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>684154</t>
+          <t>798044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1592141</t>
+          <t>1574606</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1568877</t>
+          <t>1559181</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1611923</t>
+          <t>1587426</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>152702</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>115766</t>
+          <t>133411</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>182537</t>
+          <t>188991</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>386125</t>
+          <t>422455</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>325032</t>
+          <t>389366</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>430155</t>
+          <t>457124</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>538827</t>
+          <t>582717</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>470235</t>
+          <t>545152</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>597952</t>
+          <t>628725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3304178</t>
+          <t>3367810</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3274343</t>
+          <t>3339082</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3341114</t>
+          <t>3394662</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3269043</t>
+          <t>3306783</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3225013</t>
+          <t>3272114</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3330136</t>
+          <t>3339872</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6573221</t>
+          <t>6674593</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6514096</t>
+          <t>6628585</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6641813</t>
+          <t>6712158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456880</t>
+          <t>3528073</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3655168</t>
+          <t>3729238</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7112048</t>
+          <t>7257310</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
